--- a/testdata/execute.xlsx
+++ b/testdata/execute.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$165</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$169</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1209" uniqueCount="340">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1268" uniqueCount="353">
   <si>
     <t>App</t>
   </si>
@@ -1033,6 +1033,45 @@
   </si>
   <si>
     <t>C70943</t>
+  </si>
+  <si>
+    <t>Payments-Own_Account_Transfer-From_Current_Account_RSD_To_Current_Account_RSD_[MOB_ANDROID]-To_Current_Authorized_Account</t>
+  </si>
+  <si>
+    <t>C70944</t>
+  </si>
+  <si>
+    <t>Credit_Cards_Transactions_List_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70945</t>
+  </si>
+  <si>
+    <t>Credit_Cards_Transactions_Details_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70946</t>
+  </si>
+  <si>
+    <t>C70947</t>
+  </si>
+  <si>
+    <t>Current_Accounts_RSD_Statemants_Share_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70948</t>
+  </si>
+  <si>
+    <t>Current_Foreign_Accounts_Statemants_Share_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70949</t>
+  </si>
+  <si>
+    <t>Savings_Accounts_Statemants_Share_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70950</t>
   </si>
   <si>
     <t>Automated Test Names</t>
@@ -1780,7 +1819,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1807,6 +1846,7 @@
       <alignment wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2145,7 +2185,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G200"/>
+  <dimension ref="A1:G223"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="6"/>
   <cols>
     <col min="2" max="2" width="112.574074074074" customWidth="1"/>
@@ -4127,7 +4167,7 @@
         <v>12</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="87" customFormat="1" spans="1:7">
@@ -4173,7 +4213,7 @@
         <v>12</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="89" customFormat="1" spans="1:7">
@@ -4679,7 +4719,7 @@
         <v>12</v>
       </c>
       <c r="G110" s="6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="111" customFormat="1" spans="1:7">
@@ -5047,7 +5087,7 @@
         <v>12</v>
       </c>
       <c r="G126" s="6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="127" customFormat="1" spans="1:7">
@@ -5718,7 +5758,9 @@
       </c>
     </row>
     <row r="156" customFormat="1" spans="1:7">
-      <c r="A156" s="6"/>
+      <c r="A156" s="6" t="s">
+        <v>7</v>
+      </c>
       <c r="B156" s="10" t="s">
         <v>314</v>
       </c>
@@ -5739,7 +5781,9 @@
       </c>
     </row>
     <row r="157" customFormat="1" spans="1:7">
-      <c r="A157" s="6"/>
+      <c r="A157" s="6" t="s">
+        <v>7</v>
+      </c>
       <c r="B157" s="10" t="s">
         <v>316</v>
       </c>
@@ -5760,7 +5804,9 @@
       </c>
     </row>
     <row r="158" customFormat="1" spans="1:7">
-      <c r="A158" s="6"/>
+      <c r="A158" s="6" t="s">
+        <v>7</v>
+      </c>
       <c r="B158" s="10" t="s">
         <v>318</v>
       </c>
@@ -5781,7 +5827,9 @@
       </c>
     </row>
     <row r="159" customFormat="1" spans="1:7">
-      <c r="A159" s="6"/>
+      <c r="A159" s="6" t="s">
+        <v>7</v>
+      </c>
       <c r="B159" s="10" t="s">
         <v>320</v>
       </c>
@@ -5802,7 +5850,9 @@
       </c>
     </row>
     <row r="160" customFormat="1" spans="1:7">
-      <c r="A160" s="6"/>
+      <c r="A160" s="6" t="s">
+        <v>7</v>
+      </c>
       <c r="B160" s="10" t="s">
         <v>322</v>
       </c>
@@ -5823,7 +5873,9 @@
       </c>
     </row>
     <row r="161" customFormat="1" spans="1:7">
-      <c r="A161" s="6"/>
+      <c r="A161" s="6" t="s">
+        <v>7</v>
+      </c>
       <c r="B161" s="10" t="s">
         <v>324</v>
       </c>
@@ -5844,7 +5896,9 @@
       </c>
     </row>
     <row r="162" customFormat="1" spans="1:7">
-      <c r="A162" s="6"/>
+      <c r="A162" s="6" t="s">
+        <v>7</v>
+      </c>
       <c r="B162" s="10" t="s">
         <v>326</v>
       </c>
@@ -5865,7 +5919,9 @@
       </c>
     </row>
     <row r="163" spans="1:7">
-      <c r="A163" s="6"/>
+      <c r="A163" s="6" t="s">
+        <v>7</v>
+      </c>
       <c r="B163" s="10" t="s">
         <v>328</v>
       </c>
@@ -5886,7 +5942,9 @@
       </c>
     </row>
     <row r="164" spans="1:7">
-      <c r="A164" s="6"/>
+      <c r="A164" s="6" t="s">
+        <v>7</v>
+      </c>
       <c r="B164" s="10" t="s">
         <v>330</v>
       </c>
@@ -5907,7 +5965,9 @@
       </c>
     </row>
     <row r="165" spans="1:7">
-      <c r="A165" s="6"/>
+      <c r="A165" s="6" t="s">
+        <v>7</v>
+      </c>
       <c r="B165" s="10" t="s">
         <v>332</v>
       </c>
@@ -5927,323 +5987,628 @@
         <v>13</v>
       </c>
     </row>
-    <row r="166" spans="1:7">
-      <c r="A166" s="6"/>
-      <c r="B166" s="10"/>
-      <c r="C166" s="6"/>
-      <c r="D166" s="6"/>
-      <c r="E166" s="6"/>
-      <c r="F166" s="6"/>
-      <c r="G166" s="6"/>
-    </row>
-    <row r="167" spans="1:7">
-      <c r="A167" s="6"/>
-      <c r="B167" s="10"/>
-      <c r="C167" s="6"/>
-      <c r="D167" s="6"/>
-      <c r="E167" s="6"/>
-      <c r="F167" s="6"/>
-      <c r="G167" s="6"/>
-    </row>
-    <row r="168" spans="1:7">
-      <c r="A168" s="6"/>
-      <c r="B168" s="10"/>
-      <c r="C168" s="6"/>
-      <c r="D168" s="6"/>
-      <c r="E168" s="6"/>
-      <c r="F168" s="6"/>
-      <c r="G168" s="6"/>
-    </row>
-    <row r="169" spans="1:7">
-      <c r="A169" s="6"/>
-      <c r="B169" s="10"/>
-      <c r="C169" s="6"/>
-      <c r="D169" s="6"/>
-      <c r="E169" s="6"/>
-      <c r="F169" s="6"/>
-      <c r="G169" s="6"/>
-    </row>
-    <row r="170" spans="1:7">
-      <c r="A170" s="6"/>
-      <c r="B170" s="10"/>
-      <c r="C170" s="6"/>
-      <c r="D170" s="6"/>
-      <c r="E170" s="6"/>
-      <c r="F170" s="6"/>
-      <c r="G170" s="6"/>
-    </row>
-    <row r="171" spans="1:7">
-      <c r="A171" s="6"/>
-      <c r="B171" s="10"/>
-      <c r="C171" s="6"/>
-      <c r="D171" s="6"/>
-      <c r="E171" s="6"/>
-      <c r="F171" s="6"/>
-      <c r="G171" s="6"/>
-    </row>
-    <row r="172" spans="1:7">
-      <c r="A172" s="6"/>
-      <c r="B172" s="10"/>
-      <c r="C172" s="6"/>
-      <c r="D172" s="6"/>
-      <c r="E172" s="6"/>
-      <c r="F172" s="6"/>
-      <c r="G172" s="6"/>
-    </row>
-    <row r="173" spans="1:7">
+    <row r="166" ht="28.8" spans="1:7">
+      <c r="A166" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B166" s="10" t="s">
+        <v>334</v>
+      </c>
+      <c r="C166" s="6" t="s">
+        <v>335</v>
+      </c>
+      <c r="D166" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E166" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F166" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G166" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="167" customFormat="1" spans="1:7">
+      <c r="A167" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B167" s="6" t="s">
+        <v>336</v>
+      </c>
+      <c r="C167" s="6" t="s">
+        <v>337</v>
+      </c>
+      <c r="D167" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E167" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F167" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G167" s="14" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="168" customFormat="1" spans="1:7">
+      <c r="A168" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B168" s="6" t="s">
+        <v>338</v>
+      </c>
+      <c r="C168" s="6" t="s">
+        <v>339</v>
+      </c>
+      <c r="D168" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E168" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F168" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G168" s="14" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="169" customFormat="1" spans="1:7">
+      <c r="A169" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B169" s="6" t="s">
+        <v>330</v>
+      </c>
+      <c r="C169" s="6" t="s">
+        <v>340</v>
+      </c>
+      <c r="D169" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E169" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F169" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G169" s="14" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="170" customFormat="1" spans="1:7">
+      <c r="A170" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B170" s="6" t="s">
+        <v>341</v>
+      </c>
+      <c r="C170" s="6" t="s">
+        <v>342</v>
+      </c>
+      <c r="D170" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E170" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F170" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G170" s="14" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="171" customFormat="1" spans="1:7">
+      <c r="A171" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B171" s="6" t="s">
+        <v>343</v>
+      </c>
+      <c r="C171" s="6" t="s">
+        <v>344</v>
+      </c>
+      <c r="D171" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E171" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F171" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G171" s="14" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="172" customFormat="1" spans="1:7">
+      <c r="A172" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B172" s="6" t="s">
+        <v>345</v>
+      </c>
+      <c r="C172" s="6" t="s">
+        <v>346</v>
+      </c>
+      <c r="D172" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E172" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F172" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G172" s="14" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="173" customFormat="1" spans="1:7">
       <c r="A173" s="6"/>
-      <c r="B173" s="10"/>
+      <c r="B173" s="6"/>
       <c r="C173" s="6"/>
       <c r="D173" s="6"/>
       <c r="E173" s="6"/>
-      <c r="F173" s="6"/>
+      <c r="F173" s="8"/>
       <c r="G173" s="6"/>
     </row>
-    <row r="174" spans="1:7">
+    <row r="174" customFormat="1" spans="1:7">
       <c r="A174" s="6"/>
-      <c r="B174" s="10"/>
+      <c r="B174" s="6"/>
       <c r="C174" s="6"/>
       <c r="D174" s="6"/>
       <c r="E174" s="6"/>
-      <c r="F174" s="6"/>
+      <c r="F174" s="8"/>
       <c r="G174" s="6"/>
     </row>
-    <row r="175" spans="1:7">
+    <row r="175" customFormat="1" spans="1:7">
       <c r="A175" s="6"/>
-      <c r="B175" s="10"/>
+      <c r="B175" s="6"/>
       <c r="C175" s="6"/>
       <c r="D175" s="6"/>
       <c r="E175" s="6"/>
-      <c r="F175" s="6"/>
+      <c r="F175" s="8"/>
       <c r="G175" s="6"/>
     </row>
-    <row r="176" spans="1:7">
+    <row r="176" customFormat="1" spans="1:7">
       <c r="A176" s="6"/>
-      <c r="B176" s="10"/>
+      <c r="B176" s="6"/>
       <c r="C176" s="6"/>
       <c r="D176" s="6"/>
       <c r="E176" s="6"/>
-      <c r="F176" s="6"/>
+      <c r="F176" s="8"/>
       <c r="G176" s="6"/>
     </row>
-    <row r="177" spans="1:7">
+    <row r="177" customFormat="1" spans="1:7">
       <c r="A177" s="6"/>
-      <c r="B177" s="10"/>
+      <c r="B177" s="6"/>
       <c r="C177" s="6"/>
       <c r="D177" s="6"/>
       <c r="E177" s="6"/>
-      <c r="F177" s="6"/>
+      <c r="F177" s="8"/>
       <c r="G177" s="6"/>
     </row>
-    <row r="178" spans="1:7">
+    <row r="178" customFormat="1" spans="1:7">
       <c r="A178" s="6"/>
-      <c r="B178" s="10"/>
+      <c r="B178" s="6"/>
       <c r="C178" s="6"/>
       <c r="D178" s="6"/>
       <c r="E178" s="6"/>
-      <c r="F178" s="6"/>
+      <c r="F178" s="8"/>
       <c r="G178" s="6"/>
     </row>
-    <row r="179" spans="1:7">
+    <row r="179" customFormat="1" spans="1:7">
       <c r="A179" s="6"/>
-      <c r="B179" s="10"/>
+      <c r="B179" s="6"/>
       <c r="C179" s="6"/>
       <c r="D179" s="6"/>
       <c r="E179" s="6"/>
-      <c r="F179" s="6"/>
+      <c r="F179" s="8"/>
       <c r="G179" s="6"/>
     </row>
-    <row r="180" spans="1:7">
+    <row r="180" customFormat="1" spans="1:7">
       <c r="A180" s="6"/>
-      <c r="B180" s="10"/>
+      <c r="B180" s="6"/>
       <c r="C180" s="6"/>
       <c r="D180" s="6"/>
       <c r="E180" s="6"/>
-      <c r="F180" s="6"/>
+      <c r="F180" s="8"/>
       <c r="G180" s="6"/>
     </row>
-    <row r="181" spans="1:7">
+    <row r="181" customFormat="1" spans="1:7">
       <c r="A181" s="6"/>
-      <c r="B181" s="10"/>
+      <c r="B181" s="6"/>
       <c r="C181" s="6"/>
       <c r="D181" s="6"/>
       <c r="E181" s="6"/>
-      <c r="F181" s="6"/>
+      <c r="F181" s="8"/>
       <c r="G181" s="6"/>
     </row>
-    <row r="182" spans="1:7">
+    <row r="182" customFormat="1" spans="1:7">
       <c r="A182" s="6"/>
-      <c r="B182" s="10"/>
+      <c r="B182" s="6"/>
       <c r="C182" s="6"/>
       <c r="D182" s="6"/>
       <c r="E182" s="6"/>
-      <c r="F182" s="6"/>
+      <c r="F182" s="8"/>
       <c r="G182" s="6"/>
     </row>
-    <row r="183" spans="1:7">
+    <row r="183" customFormat="1" spans="1:7">
       <c r="A183" s="6"/>
-      <c r="B183" s="10"/>
+      <c r="B183" s="6"/>
       <c r="C183" s="6"/>
       <c r="D183" s="6"/>
       <c r="E183" s="6"/>
-      <c r="F183" s="6"/>
+      <c r="F183" s="8"/>
       <c r="G183" s="6"/>
     </row>
-    <row r="184" spans="1:7">
+    <row r="184" customFormat="1" spans="1:7">
       <c r="A184" s="6"/>
-      <c r="B184" s="10"/>
+      <c r="B184" s="6"/>
       <c r="C184" s="6"/>
       <c r="D184" s="6"/>
       <c r="E184" s="6"/>
-      <c r="F184" s="6"/>
+      <c r="F184" s="8"/>
       <c r="G184" s="6"/>
     </row>
-    <row r="185" spans="1:7">
+    <row r="185" customFormat="1" spans="1:7">
       <c r="A185" s="6"/>
-      <c r="B185" s="10"/>
+      <c r="B185" s="6"/>
       <c r="C185" s="6"/>
       <c r="D185" s="6"/>
       <c r="E185" s="6"/>
-      <c r="F185" s="6"/>
+      <c r="F185" s="8"/>
       <c r="G185" s="6"/>
     </row>
-    <row r="186" spans="1:7">
+    <row r="186" customFormat="1" spans="1:7">
       <c r="A186" s="6"/>
-      <c r="B186" s="10"/>
+      <c r="B186" s="6"/>
       <c r="C186" s="6"/>
       <c r="D186" s="6"/>
       <c r="E186" s="6"/>
-      <c r="F186" s="6"/>
+      <c r="F186" s="8"/>
       <c r="G186" s="6"/>
     </row>
-    <row r="187" spans="1:7">
+    <row r="187" customFormat="1" spans="1:7">
       <c r="A187" s="6"/>
-      <c r="B187" s="10"/>
+      <c r="B187" s="6"/>
       <c r="C187" s="6"/>
       <c r="D187" s="6"/>
       <c r="E187" s="6"/>
-      <c r="F187" s="6"/>
+      <c r="F187" s="8"/>
       <c r="G187" s="6"/>
     </row>
-    <row r="188" spans="1:7">
+    <row r="188" customFormat="1" spans="1:7">
       <c r="A188" s="6"/>
-      <c r="B188" s="10"/>
+      <c r="B188" s="6"/>
       <c r="C188" s="6"/>
       <c r="D188" s="6"/>
       <c r="E188" s="6"/>
-      <c r="F188" s="6"/>
+      <c r="F188" s="8"/>
       <c r="G188" s="6"/>
     </row>
-    <row r="189" spans="1:7">
+    <row r="189" customFormat="1" spans="1:7">
       <c r="A189" s="6"/>
-      <c r="B189" s="10"/>
+      <c r="B189" s="6"/>
       <c r="C189" s="6"/>
       <c r="D189" s="6"/>
       <c r="E189" s="6"/>
-      <c r="F189" s="6"/>
+      <c r="F189" s="8"/>
       <c r="G189" s="6"/>
     </row>
-    <row r="190" spans="1:7">
+    <row r="190" customFormat="1" spans="1:7">
       <c r="A190" s="6"/>
-      <c r="B190" s="10"/>
+      <c r="B190" s="6"/>
       <c r="C190" s="6"/>
       <c r="D190" s="6"/>
       <c r="E190" s="6"/>
-      <c r="F190" s="6"/>
+      <c r="F190" s="8"/>
       <c r="G190" s="6"/>
     </row>
-    <row r="191" spans="1:7">
+    <row r="191" customFormat="1" spans="1:7">
       <c r="A191" s="6"/>
-      <c r="B191" s="10"/>
+      <c r="B191" s="6"/>
       <c r="C191" s="6"/>
       <c r="D191" s="6"/>
       <c r="E191" s="6"/>
-      <c r="F191" s="6"/>
+      <c r="F191" s="8"/>
       <c r="G191" s="6"/>
     </row>
-    <row r="192" spans="1:7">
+    <row r="192" customFormat="1" spans="1:7">
       <c r="A192" s="6"/>
-      <c r="B192" s="10"/>
+      <c r="B192" s="6"/>
       <c r="C192" s="6"/>
       <c r="D192" s="6"/>
       <c r="E192" s="6"/>
-      <c r="F192" s="6"/>
+      <c r="F192" s="8"/>
       <c r="G192" s="6"/>
     </row>
-    <row r="193" spans="1:7">
+    <row r="193" customFormat="1" spans="1:7">
       <c r="A193" s="6"/>
-      <c r="B193" s="10"/>
+      <c r="B193" s="6"/>
       <c r="C193" s="6"/>
       <c r="D193" s="6"/>
       <c r="E193" s="6"/>
-      <c r="F193" s="6"/>
+      <c r="F193" s="8"/>
       <c r="G193" s="6"/>
     </row>
-    <row r="194" spans="1:7">
+    <row r="194" customFormat="1" spans="1:7">
       <c r="A194" s="6"/>
-      <c r="B194" s="10"/>
+      <c r="B194" s="6"/>
       <c r="C194" s="6"/>
       <c r="D194" s="6"/>
       <c r="E194" s="6"/>
-      <c r="F194" s="6"/>
+      <c r="F194" s="8"/>
       <c r="G194" s="6"/>
     </row>
-    <row r="195" spans="1:7">
+    <row r="195" customFormat="1" spans="1:7">
       <c r="A195" s="6"/>
       <c r="B195" s="6"/>
       <c r="C195" s="6"/>
       <c r="D195" s="6"/>
       <c r="E195" s="6"/>
-      <c r="F195" s="6"/>
+      <c r="F195" s="8"/>
       <c r="G195" s="6"/>
     </row>
-    <row r="196" spans="1:7">
+    <row r="196" customFormat="1" spans="1:7">
       <c r="A196" s="6"/>
       <c r="B196" s="6"/>
       <c r="C196" s="6"/>
       <c r="D196" s="6"/>
       <c r="E196" s="6"/>
-      <c r="F196" s="6"/>
+      <c r="F196" s="8"/>
       <c r="G196" s="6"/>
     </row>
-    <row r="197" spans="1:7">
+    <row r="197" customFormat="1" spans="1:7">
       <c r="A197" s="6"/>
       <c r="B197" s="6"/>
       <c r="C197" s="6"/>
       <c r="D197" s="6"/>
       <c r="E197" s="6"/>
-      <c r="F197" s="6"/>
+      <c r="F197" s="8"/>
       <c r="G197" s="6"/>
     </row>
-    <row r="198" spans="1:7">
+    <row r="198" customFormat="1" spans="1:7">
       <c r="A198" s="6"/>
       <c r="B198" s="6"/>
       <c r="C198" s="6"/>
       <c r="D198" s="6"/>
       <c r="E198" s="6"/>
-      <c r="F198" s="6"/>
+      <c r="F198" s="8"/>
       <c r="G198" s="6"/>
     </row>
-    <row r="199" spans="1:7">
+    <row r="199" customFormat="1" spans="1:7">
       <c r="A199" s="6"/>
       <c r="B199" s="6"/>
       <c r="C199" s="6"/>
       <c r="D199" s="6"/>
       <c r="E199" s="6"/>
-      <c r="F199" s="6"/>
+      <c r="F199" s="8"/>
       <c r="G199" s="6"/>
     </row>
-    <row r="200" spans="1:7">
+    <row r="200" customFormat="1" spans="1:7">
       <c r="A200" s="6"/>
       <c r="B200" s="6"/>
       <c r="C200" s="6"/>
       <c r="D200" s="6"/>
       <c r="E200" s="6"/>
-      <c r="F200" s="6"/>
+      <c r="F200" s="8"/>
       <c r="G200" s="6"/>
     </row>
+    <row r="201" customFormat="1" spans="1:7">
+      <c r="A201" s="6"/>
+      <c r="B201" s="6"/>
+      <c r="C201" s="6"/>
+      <c r="D201" s="6"/>
+      <c r="E201" s="6"/>
+      <c r="F201" s="8"/>
+      <c r="G201" s="6"/>
+    </row>
+    <row r="202" customFormat="1" spans="1:7">
+      <c r="A202" s="6"/>
+      <c r="B202" s="6"/>
+      <c r="C202" s="6"/>
+      <c r="D202" s="6"/>
+      <c r="E202" s="6"/>
+      <c r="F202" s="8"/>
+      <c r="G202" s="6"/>
+    </row>
+    <row r="203" customFormat="1" spans="1:7">
+      <c r="A203" s="6"/>
+      <c r="B203" s="6"/>
+      <c r="C203" s="6"/>
+      <c r="D203" s="6"/>
+      <c r="E203" s="6"/>
+      <c r="F203" s="8"/>
+      <c r="G203" s="6"/>
+    </row>
+    <row r="204" customFormat="1" spans="1:7">
+      <c r="A204" s="6"/>
+      <c r="B204" s="6"/>
+      <c r="C204" s="6"/>
+      <c r="D204" s="6"/>
+      <c r="E204" s="6"/>
+      <c r="F204" s="8"/>
+      <c r="G204" s="6"/>
+    </row>
+    <row r="205" customFormat="1" spans="1:7">
+      <c r="A205" s="6"/>
+      <c r="B205" s="6"/>
+      <c r="C205" s="6"/>
+      <c r="D205" s="6"/>
+      <c r="E205" s="6"/>
+      <c r="F205" s="8"/>
+      <c r="G205" s="6"/>
+    </row>
+    <row r="206" customFormat="1" spans="1:7">
+      <c r="A206" s="6"/>
+      <c r="B206" s="6"/>
+      <c r="C206" s="6"/>
+      <c r="D206" s="6"/>
+      <c r="E206" s="6"/>
+      <c r="F206" s="8"/>
+      <c r="G206" s="6"/>
+    </row>
+    <row r="207" customFormat="1" spans="1:7">
+      <c r="A207" s="6"/>
+      <c r="B207" s="6"/>
+      <c r="C207" s="6"/>
+      <c r="D207" s="6"/>
+      <c r="E207" s="6"/>
+      <c r="F207" s="8"/>
+      <c r="G207" s="6"/>
+    </row>
+    <row r="208" customFormat="1" spans="1:7">
+      <c r="A208" s="6"/>
+      <c r="B208" s="6"/>
+      <c r="C208" s="6"/>
+      <c r="D208" s="6"/>
+      <c r="E208" s="6"/>
+      <c r="F208" s="8"/>
+      <c r="G208" s="6"/>
+    </row>
+    <row r="209" customFormat="1" spans="1:7">
+      <c r="A209" s="6"/>
+      <c r="B209" s="6"/>
+      <c r="C209" s="6"/>
+      <c r="D209" s="6"/>
+      <c r="E209" s="6"/>
+      <c r="F209" s="8"/>
+      <c r="G209" s="6"/>
+    </row>
+    <row r="210" customFormat="1" spans="1:7">
+      <c r="A210" s="6"/>
+      <c r="B210" s="6"/>
+      <c r="C210" s="6"/>
+      <c r="D210" s="6"/>
+      <c r="E210" s="6"/>
+      <c r="F210" s="8"/>
+      <c r="G210" s="6"/>
+    </row>
+    <row r="211" customFormat="1" spans="1:7">
+      <c r="A211" s="6"/>
+      <c r="B211" s="6"/>
+      <c r="C211" s="6"/>
+      <c r="D211" s="6"/>
+      <c r="E211" s="6"/>
+      <c r="F211" s="8"/>
+      <c r="G211" s="6"/>
+    </row>
+    <row r="212" customFormat="1" spans="1:7">
+      <c r="A212" s="6"/>
+      <c r="B212" s="6"/>
+      <c r="C212" s="6"/>
+      <c r="D212" s="6"/>
+      <c r="E212" s="6"/>
+      <c r="F212" s="8"/>
+      <c r="G212" s="6"/>
+    </row>
+    <row r="213" customFormat="1" spans="1:7">
+      <c r="A213" s="6"/>
+      <c r="B213" s="6"/>
+      <c r="C213" s="6"/>
+      <c r="D213" s="6"/>
+      <c r="E213" s="6"/>
+      <c r="F213" s="8"/>
+      <c r="G213" s="6"/>
+    </row>
+    <row r="214" customFormat="1" spans="1:7">
+      <c r="A214" s="6"/>
+      <c r="B214" s="6"/>
+      <c r="C214" s="6"/>
+      <c r="D214" s="6"/>
+      <c r="E214" s="6"/>
+      <c r="F214" s="8"/>
+      <c r="G214" s="6"/>
+    </row>
+    <row r="215" customFormat="1" spans="1:7">
+      <c r="A215" s="6"/>
+      <c r="B215" s="6"/>
+      <c r="C215" s="6"/>
+      <c r="D215" s="6"/>
+      <c r="E215" s="6"/>
+      <c r="F215" s="8"/>
+      <c r="G215" s="6"/>
+    </row>
+    <row r="216" customFormat="1" spans="1:7">
+      <c r="A216" s="6"/>
+      <c r="B216" s="6"/>
+      <c r="C216" s="6"/>
+      <c r="D216" s="6"/>
+      <c r="E216" s="6"/>
+      <c r="F216" s="8"/>
+      <c r="G216" s="6"/>
+    </row>
+    <row r="217" customFormat="1" spans="1:7">
+      <c r="A217" s="6"/>
+      <c r="B217" s="6"/>
+      <c r="C217" s="6"/>
+      <c r="D217" s="6"/>
+      <c r="E217" s="6"/>
+      <c r="F217" s="8"/>
+      <c r="G217" s="6"/>
+    </row>
+    <row r="218" customFormat="1" spans="1:7">
+      <c r="A218" s="6"/>
+      <c r="B218" s="6"/>
+      <c r="C218" s="6"/>
+      <c r="D218" s="6"/>
+      <c r="E218" s="6"/>
+      <c r="F218" s="8"/>
+      <c r="G218" s="6"/>
+    </row>
+    <row r="219" customFormat="1" spans="1:7">
+      <c r="A219" s="6"/>
+      <c r="B219" s="6"/>
+      <c r="C219" s="6"/>
+      <c r="D219" s="6"/>
+      <c r="E219" s="6"/>
+      <c r="F219" s="8"/>
+      <c r="G219" s="6"/>
+    </row>
+    <row r="220" customFormat="1" spans="1:7">
+      <c r="A220" s="6"/>
+      <c r="B220" s="6"/>
+      <c r="C220" s="6"/>
+      <c r="D220" s="6"/>
+      <c r="E220" s="6"/>
+      <c r="F220" s="8"/>
+      <c r="G220" s="6"/>
+    </row>
+    <row r="221" customFormat="1" spans="1:7">
+      <c r="A221" s="6"/>
+      <c r="B221" s="6"/>
+      <c r="C221" s="6"/>
+      <c r="D221" s="6"/>
+      <c r="E221" s="6"/>
+      <c r="F221" s="8"/>
+      <c r="G221" s="6"/>
+    </row>
+    <row r="222" customFormat="1" spans="1:7">
+      <c r="A222" s="6"/>
+      <c r="B222" s="6"/>
+      <c r="C222" s="6"/>
+      <c r="D222" s="6"/>
+      <c r="E222" s="6"/>
+      <c r="F222" s="8"/>
+      <c r="G222" s="6"/>
+    </row>
+    <row r="223" customFormat="1" spans="1:7">
+      <c r="A223" s="6"/>
+      <c r="B223" s="6"/>
+      <c r="C223" s="6"/>
+      <c r="D223" s="6"/>
+      <c r="E223" s="6"/>
+      <c r="F223" s="8"/>
+      <c r="G223" s="6"/>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G165" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G169" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <conditionalFormatting sqref="C$1:C$1048576">
@@ -6271,7 +6636,7 @@
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="15.15" spans="1:4">
       <c r="A1" s="2" t="s">
-        <v>334</v>
+        <v>347</v>
       </c>
       <c r="B1"/>
       <c r="C1"/>
@@ -6407,7 +6772,7 @@
     </row>
     <row r="18" s="1" customFormat="1" ht="15.15" spans="1:4">
       <c r="A18" s="3" t="s">
-        <v>335</v>
+        <v>348</v>
       </c>
       <c r="B18"/>
       <c r="C18"/>
@@ -6423,7 +6788,7 @@
     </row>
     <row r="20" s="1" customFormat="1" ht="15.15" spans="1:4">
       <c r="A20" s="3" t="s">
-        <v>336</v>
+        <v>349</v>
       </c>
       <c r="B20"/>
       <c r="C20"/>
@@ -6535,7 +6900,7 @@
     </row>
     <row r="34" s="1" customFormat="1" ht="15.15" spans="1:4">
       <c r="A34" s="3" t="s">
-        <v>337</v>
+        <v>350</v>
       </c>
       <c r="B34"/>
       <c r="C34"/>
@@ -6618,7 +6983,7 @@
     </row>
     <row r="47" ht="15.15" spans="1:4">
       <c r="A47" s="3" t="s">
-        <v>338</v>
+        <v>351</v>
       </c>
     </row>
     <row r="48" ht="15.15" spans="1:4">
@@ -6658,7 +7023,7 @@
     </row>
     <row r="55" ht="15.15" spans="1:1">
       <c r="A55" s="3" t="s">
-        <v>339</v>
+        <v>352</v>
       </c>
     </row>
     <row r="56" ht="15.15" spans="1:1">

--- a/testdata/execute.xlsx
+++ b/testdata/execute.xlsx
@@ -4,14 +4,14 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9000"/>
+    <workbookView windowWidth="22728" windowHeight="8964"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$169</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$174</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1268" uniqueCount="353">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1366" uniqueCount="380">
   <si>
     <t>App</t>
   </si>
@@ -81,21 +81,21 @@
     <t>C70780</t>
   </si>
   <si>
+    <t>Product_Summary_Sorting_on_the_Product_Summary_[ANDROID]</t>
+  </si>
+  <si>
+    <t>C70781</t>
+  </si>
+  <si>
+    <t>Product_Summary-Edit_Product_view-edit_name_of_account-invalid_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70782</t>
+  </si>
+  <si>
     <t>off</t>
   </si>
   <si>
-    <t>Product_Summary_Sorting_on_the_Product_Summary_[ANDROID]</t>
-  </si>
-  <si>
-    <t>C70781</t>
-  </si>
-  <si>
-    <t>Product_Summary-Edit_Product_view-edit_name_of_account-invalid_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70782</t>
-  </si>
-  <si>
     <t>Product_Summary-Edit_Product_view-edit_name_of_account-invalid_[MOB_ANDROID]_6</t>
   </si>
   <si>
@@ -1074,6 +1074,90 @@
     <t>C70950</t>
   </si>
   <si>
+    <t>Authentication_Mobile_Login_Forgot_PIN_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70951</t>
+  </si>
+  <si>
+    <t>Domestic_Payments_Budzetski_Non_Urgent_Payment_Model97_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70952</t>
+  </si>
+  <si>
+    <t>Savings_Accounts_Transactions_Filter_By_Date_Date_Picker_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70953</t>
+  </si>
+  <si>
+    <t>Savings_Accounts_Transactions_Filter_Filter_By_Type_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70954</t>
+  </si>
+  <si>
+    <t>Savings_Accounts_Transactions_Filter_By_Amount_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70955</t>
+  </si>
+  <si>
+    <t>Savings_Accounts_Transactions_Filter_By_Date_Date_Picker_Invalid_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70956</t>
+  </si>
+  <si>
+    <t>Savings_Accounts_Transactions_Filter_Multiple_Filter_Invalid_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70957</t>
+  </si>
+  <si>
+    <t>Savings_Accounts_Transactions_Search_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70958</t>
+  </si>
+  <si>
+    <t>Credit_Cards_Transactions_Filter_By_Date_Predefined_Date_Range_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70959</t>
+  </si>
+  <si>
+    <t>Loan_Accounts_Header_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70960</t>
+  </si>
+  <si>
+    <t>Payments-Domestic_Payments_Input_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70961</t>
+  </si>
+  <si>
+    <t>Manage_Products_Favorite_account_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70962</t>
+  </si>
+  <si>
+    <t>Manage_Products_Favorite_account_[MOB_ANDROID]-Removal_Of_The_Favorite_Account</t>
+  </si>
+  <si>
+    <t>C70963</t>
+  </si>
+  <si>
+    <t>Credit_Cards-Transactions-Filter-Filter_By_Status_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70964</t>
+  </si>
+  <si>
     <t>Automated Test Names</t>
   </si>
   <si>
@@ -1084,9 +1168,6 @@
   </si>
   <si>
     <t>Payments_Domestic_Payments_Internal_Urgent_Payment_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>Domestic_Payments_Budzetski_Non_Urgent_Payment_Model97_[MOB_ANDROID]</t>
   </si>
   <si>
     <t>Manage_Products_Nickname_Product_[MOB_ANDROID]</t>
@@ -1819,7 +1900,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1846,7 +1927,11 @@
       <alignment wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2258,7 +2343,7 @@
         <v>12</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" customFormat="1" spans="1:7">
@@ -2266,10 +2351,10 @@
         <v>7</v>
       </c>
       <c r="B4" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="6" t="s">
         <v>17</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>18</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>10</v>
@@ -2289,22 +2374,22 @@
         <v>7</v>
       </c>
       <c r="B5" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="D5" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" s="6" t="s">
         <v>20</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="6" customFormat="1" spans="1:7">
@@ -2327,7 +2412,7 @@
         <v>12</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" customFormat="1" spans="1:7">
@@ -2350,7 +2435,7 @@
         <v>12</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" customFormat="1" spans="1:7">
@@ -2373,7 +2458,7 @@
         <v>12</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" customFormat="1" spans="1:7">
@@ -2396,7 +2481,7 @@
         <v>12</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10" customFormat="1" spans="1:7">
@@ -2419,7 +2504,7 @@
         <v>12</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11" customFormat="1" spans="1:7">
@@ -2442,7 +2527,7 @@
         <v>12</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12" customFormat="1" spans="1:7">
@@ -2465,7 +2550,7 @@
         <v>12</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13" customFormat="1" spans="1:7">
@@ -2488,7 +2573,7 @@
         <v>12</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14" customFormat="1" spans="1:7">
@@ -2511,7 +2596,7 @@
         <v>12</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15" customFormat="1" spans="1:7">
@@ -2534,7 +2619,7 @@
         <v>12</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16" customFormat="1" spans="1:7">
@@ -2557,7 +2642,7 @@
         <v>12</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17" customFormat="1" spans="1:7">
@@ -2580,7 +2665,7 @@
         <v>12</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18" customFormat="1" spans="1:7">
@@ -2603,7 +2688,7 @@
         <v>12</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19" customFormat="1" spans="1:7">
@@ -2626,7 +2711,7 @@
         <v>12</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="20" customFormat="1" spans="1:7">
@@ -2649,7 +2734,7 @@
         <v>12</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21" customFormat="1" spans="1:7">
@@ -2672,7 +2757,7 @@
         <v>12</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="22" customFormat="1" spans="1:7">
@@ -2695,7 +2780,7 @@
         <v>12</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="23" customFormat="1" spans="1:7">
@@ -2718,7 +2803,7 @@
         <v>12</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="24" customFormat="1" spans="1:7">
@@ -2741,7 +2826,7 @@
         <v>12</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="25" customFormat="1" spans="1:7">
@@ -2764,7 +2849,7 @@
         <v>12</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="26" customFormat="1" spans="1:7">
@@ -2787,7 +2872,7 @@
         <v>12</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="27" customFormat="1" spans="1:7">
@@ -2810,7 +2895,7 @@
         <v>12</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="28" customFormat="1" spans="1:7">
@@ -2833,7 +2918,7 @@
         <v>12</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="29" customFormat="1" spans="1:7">
@@ -2856,7 +2941,7 @@
         <v>12</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="30" customFormat="1" spans="1:7">
@@ -2879,7 +2964,7 @@
         <v>12</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="31" customFormat="1" spans="1:7">
@@ -2902,7 +2987,7 @@
         <v>12</v>
       </c>
       <c r="G31" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="32" customFormat="1" spans="1:7">
@@ -2925,7 +3010,7 @@
         <v>12</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="33" customFormat="1" spans="1:7">
@@ -2971,7 +3056,7 @@
         <v>12</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="35" customFormat="1" spans="1:7">
@@ -3017,7 +3102,7 @@
         <v>12</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="37" customFormat="1" spans="1:7">
@@ -3040,7 +3125,7 @@
         <v>12</v>
       </c>
       <c r="G37" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="38" customFormat="1" spans="1:7">
@@ -3086,7 +3171,7 @@
         <v>12</v>
       </c>
       <c r="G39" s="6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="40" customFormat="1" spans="1:7">
@@ -3132,7 +3217,7 @@
         <v>12</v>
       </c>
       <c r="G41" s="6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="42" customFormat="1" spans="1:7">
@@ -3155,7 +3240,7 @@
         <v>12</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="43" customFormat="1" spans="1:7">
@@ -3178,7 +3263,7 @@
         <v>12</v>
       </c>
       <c r="G43" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="44" customFormat="1" spans="1:7">
@@ -3201,7 +3286,7 @@
         <v>12</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="45" customFormat="1" spans="1:7">
@@ -3224,7 +3309,7 @@
         <v>12</v>
       </c>
       <c r="G45" s="6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="46" customFormat="1" spans="1:7">
@@ -3247,7 +3332,7 @@
         <v>12</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="47" customFormat="1" spans="1:7">
@@ -3293,7 +3378,7 @@
         <v>12</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="49" customFormat="1" spans="1:7">
@@ -3316,7 +3401,7 @@
         <v>12</v>
       </c>
       <c r="G49" s="6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="50" customFormat="1" spans="1:7">
@@ -3339,7 +3424,7 @@
         <v>12</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="51" customFormat="1" spans="1:7">
@@ -3385,7 +3470,7 @@
         <v>12</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="53" customFormat="1" spans="1:7">
@@ -3408,7 +3493,7 @@
         <v>12</v>
       </c>
       <c r="G53" s="6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="54" customFormat="1" spans="1:7">
@@ -3431,7 +3516,7 @@
         <v>12</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="55" customFormat="1" spans="1:7">
@@ -3454,7 +3539,7 @@
         <v>12</v>
       </c>
       <c r="G55" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="56" customFormat="1" spans="1:7">
@@ -3500,7 +3585,7 @@
         <v>12</v>
       </c>
       <c r="G57" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="58" customFormat="1" spans="1:7">
@@ -3523,7 +3608,7 @@
         <v>12</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="59" customFormat="1" spans="1:7">
@@ -3546,7 +3631,7 @@
         <v>12</v>
       </c>
       <c r="G59" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="60" customFormat="1" spans="1:7">
@@ -3569,7 +3654,7 @@
         <v>12</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="61" customFormat="1" spans="1:7">
@@ -3592,7 +3677,7 @@
         <v>12</v>
       </c>
       <c r="G61" s="6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="62" customFormat="1" spans="1:7">
@@ -3615,7 +3700,7 @@
         <v>12</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="63" customFormat="1" spans="1:7">
@@ -3638,7 +3723,7 @@
         <v>12</v>
       </c>
       <c r="G63" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="64" customFormat="1" spans="1:7">
@@ -3661,7 +3746,7 @@
         <v>12</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="65" customFormat="1" spans="1:7">
@@ -3684,7 +3769,7 @@
         <v>12</v>
       </c>
       <c r="G65" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="66" customFormat="1" spans="1:7">
@@ -3707,7 +3792,7 @@
         <v>12</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="67" customFormat="1" spans="1:7">
@@ -3730,7 +3815,7 @@
         <v>12</v>
       </c>
       <c r="G67" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="68" customFormat="1" spans="1:7">
@@ -3753,7 +3838,7 @@
         <v>12</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="69" customFormat="1" spans="1:7">
@@ -3776,7 +3861,7 @@
         <v>12</v>
       </c>
       <c r="G69" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="70" customFormat="1" spans="1:7">
@@ -3799,7 +3884,7 @@
         <v>12</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="71" customFormat="1" spans="1:7">
@@ -3868,7 +3953,7 @@
         <v>12</v>
       </c>
       <c r="G73" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="74" customFormat="1" spans="1:7">
@@ -3891,7 +3976,7 @@
         <v>12</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="75" customFormat="1" spans="1:7">
@@ -3914,7 +3999,7 @@
         <v>12</v>
       </c>
       <c r="G75" s="6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="76" customFormat="1" spans="1:7">
@@ -3937,7 +4022,7 @@
         <v>12</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="77" customFormat="1" spans="1:7">
@@ -3960,7 +4045,7 @@
         <v>12</v>
       </c>
       <c r="G77" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="78" customFormat="1" spans="1:7">
@@ -4006,7 +4091,7 @@
         <v>12</v>
       </c>
       <c r="G79" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="80" customFormat="1" spans="1:7">
@@ -4052,7 +4137,7 @@
         <v>12</v>
       </c>
       <c r="G81" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="82" customFormat="1" spans="1:7">
@@ -4075,7 +4160,7 @@
         <v>12</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="83" customFormat="1" spans="1:7">
@@ -4098,7 +4183,7 @@
         <v>12</v>
       </c>
       <c r="G83" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="84" customFormat="1" spans="1:7">
@@ -4121,7 +4206,7 @@
         <v>12</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="85" customFormat="1" spans="1:7">
@@ -4236,7 +4321,7 @@
         <v>12</v>
       </c>
       <c r="G89" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="90" customFormat="1" spans="1:7">
@@ -4259,7 +4344,7 @@
         <v>12</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="91" customFormat="1" spans="1:7">
@@ -4328,7 +4413,7 @@
         <v>12</v>
       </c>
       <c r="G93" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="94" customFormat="1" spans="1:7">
@@ -4351,7 +4436,7 @@
         <v>12</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="95" customFormat="1" spans="1:7">
@@ -4374,7 +4459,7 @@
         <v>12</v>
       </c>
       <c r="G95" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="96" customFormat="1" spans="1:7">
@@ -4397,7 +4482,7 @@
         <v>12</v>
       </c>
       <c r="G96" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="97" customFormat="1" spans="1:7">
@@ -4420,7 +4505,7 @@
         <v>12</v>
       </c>
       <c r="G97" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="98" customFormat="1" spans="1:7">
@@ -4466,7 +4551,7 @@
         <v>12</v>
       </c>
       <c r="G99" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="100" customFormat="1" spans="1:7">
@@ -4512,7 +4597,7 @@
         <v>12</v>
       </c>
       <c r="G101" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="102" customFormat="1" spans="1:7">
@@ -4535,7 +4620,7 @@
         <v>12</v>
       </c>
       <c r="G102" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="103" customFormat="1" spans="1:7">
@@ -4558,7 +4643,7 @@
         <v>12</v>
       </c>
       <c r="G103" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="104" customFormat="1" spans="1:7">
@@ -4581,7 +4666,7 @@
         <v>12</v>
       </c>
       <c r="G104" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="105" customFormat="1" spans="1:7">
@@ -4604,7 +4689,7 @@
         <v>12</v>
       </c>
       <c r="G105" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="106" customFormat="1" spans="1:7">
@@ -4627,7 +4712,7 @@
         <v>12</v>
       </c>
       <c r="G106" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="107" customFormat="1" spans="1:7">
@@ -4650,7 +4735,7 @@
         <v>12</v>
       </c>
       <c r="G107" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="108" customFormat="1" spans="1:7">
@@ -4673,7 +4758,7 @@
         <v>12</v>
       </c>
       <c r="G108" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="109" customFormat="1" spans="1:7">
@@ -4949,7 +5034,7 @@
         <v>12</v>
       </c>
       <c r="G120" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="121" customFormat="1" spans="1:7">
@@ -4972,7 +5057,7 @@
         <v>12</v>
       </c>
       <c r="G121" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="122" customFormat="1" spans="1:7">
@@ -5918,7 +6003,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="163" spans="1:7">
+    <row r="163" customFormat="1" spans="1:7">
       <c r="A163" s="6" t="s">
         <v>7</v>
       </c>
@@ -5941,7 +6026,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="164" spans="1:7">
+    <row r="164" customFormat="1" spans="1:7">
       <c r="A164" s="6" t="s">
         <v>7</v>
       </c>
@@ -5964,7 +6049,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="165" spans="1:7">
+    <row r="165" customFormat="1" spans="1:7">
       <c r="A165" s="6" t="s">
         <v>7</v>
       </c>
@@ -5987,7 +6072,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="166" ht="28.8" spans="1:7">
+    <row r="166" customFormat="1" ht="28.8" spans="1:7">
       <c r="A166" s="6" t="s">
         <v>7</v>
       </c>
@@ -6000,7 +6085,7 @@
       <c r="D166" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E166" s="7" t="s">
+      <c r="E166" s="14" t="s">
         <v>11</v>
       </c>
       <c r="F166" s="6" t="s">
@@ -6029,7 +6114,7 @@
       <c r="F167" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G167" s="14" t="s">
+      <c r="G167" s="15" t="s">
         <v>13</v>
       </c>
     </row>
@@ -6052,7 +6137,7 @@
       <c r="F168" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G168" s="14" t="s">
+      <c r="G168" s="15" t="s">
         <v>13</v>
       </c>
     </row>
@@ -6075,7 +6160,7 @@
       <c r="F169" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G169" s="14" t="s">
+      <c r="G169" s="15" t="s">
         <v>13</v>
       </c>
     </row>
@@ -6098,7 +6183,7 @@
       <c r="F170" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G170" s="14" t="s">
+      <c r="G170" s="15" t="s">
         <v>13</v>
       </c>
     </row>
@@ -6121,7 +6206,7 @@
       <c r="F171" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G171" s="14" t="s">
+      <c r="G171" s="15" t="s">
         <v>13</v>
       </c>
     </row>
@@ -6144,135 +6229,331 @@
       <c r="F172" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G172" s="14" t="s">
+      <c r="G172" s="15" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="173" customFormat="1" spans="1:7">
-      <c r="A173" s="6"/>
-      <c r="B173" s="6"/>
-      <c r="C173" s="6"/>
-      <c r="D173" s="6"/>
-      <c r="E173" s="6"/>
-      <c r="F173" s="8"/>
-      <c r="G173" s="6"/>
+      <c r="A173" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B173" s="6" t="s">
+        <v>347</v>
+      </c>
+      <c r="C173" s="6" t="s">
+        <v>348</v>
+      </c>
+      <c r="D173" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E173" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F173" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G173" s="15" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="174" customFormat="1" spans="1:7">
-      <c r="A174" s="6"/>
-      <c r="B174" s="6"/>
-      <c r="C174" s="6"/>
-      <c r="D174" s="6"/>
-      <c r="E174" s="6"/>
-      <c r="F174" s="8"/>
-      <c r="G174" s="6"/>
+      <c r="A174" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B174" s="6" t="s">
+        <v>349</v>
+      </c>
+      <c r="C174" s="6" t="s">
+        <v>350</v>
+      </c>
+      <c r="D174" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E174" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F174" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G174" s="15" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="175" customFormat="1" spans="1:7">
-      <c r="A175" s="6"/>
-      <c r="B175" s="6"/>
-      <c r="C175" s="6"/>
-      <c r="D175" s="6"/>
-      <c r="E175" s="6"/>
-      <c r="F175" s="8"/>
-      <c r="G175" s="6"/>
+      <c r="A175" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B175" s="6" t="s">
+        <v>351</v>
+      </c>
+      <c r="C175" s="6" t="s">
+        <v>352</v>
+      </c>
+      <c r="D175" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E175" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F175" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G175" s="15" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="176" customFormat="1" spans="1:7">
-      <c r="A176" s="6"/>
-      <c r="B176" s="6"/>
-      <c r="C176" s="6"/>
-      <c r="D176" s="6"/>
-      <c r="E176" s="6"/>
-      <c r="F176" s="8"/>
-      <c r="G176" s="6"/>
+      <c r="A176" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B176" s="6" t="s">
+        <v>353</v>
+      </c>
+      <c r="C176" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="D176" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E176" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F176" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G176" s="15" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="177" customFormat="1" spans="1:7">
-      <c r="A177" s="6"/>
-      <c r="B177" s="6"/>
-      <c r="C177" s="6"/>
-      <c r="D177" s="6"/>
-      <c r="E177" s="6"/>
-      <c r="F177" s="8"/>
-      <c r="G177" s="6"/>
+      <c r="A177" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B177" s="6" t="s">
+        <v>355</v>
+      </c>
+      <c r="C177" s="6" t="s">
+        <v>356</v>
+      </c>
+      <c r="D177" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E177" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F177" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G177" s="15" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="178" customFormat="1" spans="1:7">
-      <c r="A178" s="6"/>
-      <c r="B178" s="6"/>
-      <c r="C178" s="6"/>
-      <c r="D178" s="6"/>
-      <c r="E178" s="6"/>
-      <c r="F178" s="8"/>
-      <c r="G178" s="6"/>
+      <c r="A178" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B178" s="6" t="s">
+        <v>357</v>
+      </c>
+      <c r="C178" s="6" t="s">
+        <v>358</v>
+      </c>
+      <c r="D178" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E178" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F178" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G178" s="15" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="179" customFormat="1" spans="1:7">
-      <c r="A179" s="6"/>
-      <c r="B179" s="6"/>
-      <c r="C179" s="6"/>
-      <c r="D179" s="6"/>
-      <c r="E179" s="6"/>
-      <c r="F179" s="8"/>
-      <c r="G179" s="6"/>
+      <c r="A179" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B179" s="16" t="s">
+        <v>359</v>
+      </c>
+      <c r="C179" s="6" t="s">
+        <v>360</v>
+      </c>
+      <c r="D179" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E179" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F179" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G179" s="15" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="180" customFormat="1" spans="1:7">
-      <c r="A180" s="6"/>
-      <c r="B180" s="6"/>
-      <c r="C180" s="6"/>
-      <c r="D180" s="6"/>
-      <c r="E180" s="6"/>
-      <c r="F180" s="8"/>
-      <c r="G180" s="6"/>
+      <c r="A180" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B180" s="16" t="s">
+        <v>361</v>
+      </c>
+      <c r="C180" s="6" t="s">
+        <v>362</v>
+      </c>
+      <c r="D180" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E180" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F180" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G180" s="15" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="181" customFormat="1" spans="1:7">
-      <c r="A181" s="6"/>
-      <c r="B181" s="6"/>
-      <c r="C181" s="6"/>
-      <c r="D181" s="6"/>
-      <c r="E181" s="6"/>
-      <c r="F181" s="8"/>
-      <c r="G181" s="6"/>
+      <c r="A181" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B181" s="6" t="s">
+        <v>363</v>
+      </c>
+      <c r="C181" s="6" t="s">
+        <v>364</v>
+      </c>
+      <c r="D181" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E181" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F181" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G181" s="15" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="182" customFormat="1" spans="1:7">
-      <c r="A182" s="6"/>
-      <c r="B182" s="6"/>
-      <c r="C182" s="6"/>
-      <c r="D182" s="6"/>
-      <c r="E182" s="6"/>
-      <c r="F182" s="8"/>
-      <c r="G182" s="6"/>
+      <c r="A182" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B182" s="6" t="s">
+        <v>365</v>
+      </c>
+      <c r="C182" s="6" t="s">
+        <v>366</v>
+      </c>
+      <c r="D182" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E182" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F182" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G182" s="15" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="183" customFormat="1" spans="1:7">
-      <c r="A183" s="6"/>
-      <c r="B183" s="6"/>
-      <c r="C183" s="6"/>
-      <c r="D183" s="6"/>
-      <c r="E183" s="6"/>
-      <c r="F183" s="8"/>
-      <c r="G183" s="6"/>
+      <c r="A183" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B183" s="6" t="s">
+        <v>367</v>
+      </c>
+      <c r="C183" s="6" t="s">
+        <v>368</v>
+      </c>
+      <c r="D183" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E183" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F183" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G183" s="15" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="184" customFormat="1" spans="1:7">
-      <c r="A184" s="6"/>
-      <c r="B184" s="6"/>
-      <c r="C184" s="6"/>
-      <c r="D184" s="6"/>
-      <c r="E184" s="6"/>
-      <c r="F184" s="8"/>
-      <c r="G184" s="6"/>
+      <c r="A184" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B184" s="6" t="s">
+        <v>369</v>
+      </c>
+      <c r="C184" s="6" t="s">
+        <v>370</v>
+      </c>
+      <c r="D184" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E184" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F184" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G184" s="15" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="185" customFormat="1" spans="1:7">
-      <c r="A185" s="6"/>
-      <c r="B185" s="6"/>
-      <c r="C185" s="6"/>
-      <c r="D185" s="6"/>
-      <c r="E185" s="6"/>
-      <c r="F185" s="8"/>
-      <c r="G185" s="6"/>
+      <c r="A185" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B185" s="6" t="s">
+        <v>371</v>
+      </c>
+      <c r="C185" s="6" t="s">
+        <v>372</v>
+      </c>
+      <c r="D185" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E185" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F185" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G185" s="15" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="186" customFormat="1" spans="1:7">
-      <c r="A186" s="6"/>
-      <c r="B186" s="6"/>
-      <c r="C186" s="6"/>
-      <c r="D186" s="6"/>
-      <c r="E186" s="6"/>
-      <c r="F186" s="8"/>
-      <c r="G186" s="6"/>
+      <c r="A186" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B186" s="6" t="s">
+        <v>373</v>
+      </c>
+      <c r="C186" s="6" t="s">
+        <v>374</v>
+      </c>
+      <c r="D186" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E186" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F186" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G186" s="15" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="187" customFormat="1" spans="1:7">
       <c r="A187" s="6"/>
@@ -6608,7 +6889,7 @@
       <c r="G223" s="6"/>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G169" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G174" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <conditionalFormatting sqref="C$1:C$1048576">
@@ -6636,7 +6917,7 @@
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="15.15" spans="1:4">
       <c r="A1" s="2" t="s">
-        <v>347</v>
+        <v>375</v>
       </c>
       <c r="B1"/>
       <c r="C1"/>
@@ -6644,7 +6925,7 @@
     </row>
     <row r="2" s="1" customFormat="1" ht="15.15" spans="1:4">
       <c r="A2" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B2"/>
       <c r="C2"/>
@@ -6772,7 +7053,7 @@
     </row>
     <row r="18" s="1" customFormat="1" ht="15.15" spans="1:4">
       <c r="A18" s="3" t="s">
-        <v>348</v>
+        <v>376</v>
       </c>
       <c r="B18"/>
       <c r="C18"/>
@@ -6788,7 +7069,7 @@
     </row>
     <row r="20" s="1" customFormat="1" ht="15.15" spans="1:4">
       <c r="A20" s="3" t="s">
-        <v>349</v>
+        <v>377</v>
       </c>
       <c r="B20"/>
       <c r="C20"/>
@@ -6900,7 +7181,7 @@
     </row>
     <row r="34" s="1" customFormat="1" ht="15.15" spans="1:4">
       <c r="A34" s="3" t="s">
-        <v>350</v>
+        <v>378</v>
       </c>
       <c r="B34"/>
       <c r="C34"/>
@@ -6983,7 +7264,7 @@
     </row>
     <row r="47" ht="15.15" spans="1:4">
       <c r="A47" s="3" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="48" ht="15.15" spans="1:4">
@@ -7023,7 +7304,7 @@
     </row>
     <row r="55" ht="15.15" spans="1:1">
       <c r="A55" s="3" t="s">
-        <v>352</v>
+        <v>379</v>
       </c>
     </row>
     <row r="56" ht="15.15" spans="1:1">
